--- a/projects/lca/02_Regionalization/01_Notebooks/Data/unit_conversion.xlsx
+++ b/projects/lca/02_Regionalization/01_Notebooks/Data/unit_conversion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matth\PycharmProjects\EnergyScope-Quebec\projects\lca\02_Regionalization\01_Notebooks\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953C6B13-0CE0-4D1F-B6B6-E6A203DB506B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60ED90C3-4681-479E-8DA5-FC33419F59CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6276" uniqueCount="1045">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6276" uniqueCount="1044">
   <si>
     <t>Name</t>
   </si>
@@ -2500,9 +2500,6 @@
   </si>
   <si>
     <t>natural gas density (0.777 kg/m3): \cite{engineeringtoolbox2003}</t>
-  </si>
-  <si>
-    <t>dry wood LHV (4.28 kWh/kg): \cite{engineeringtoolbox2003}</t>
   </si>
   <si>
     <t>diesel LHV (11.83 kWh/kg): \cite{engineeringtoolbox2003}</t>
@@ -3630,7 +3627,7 @@
         <v>730</v>
       </c>
       <c r="F4" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -3668,7 +3665,7 @@
         <v>730</v>
       </c>
       <c r="F6" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -3854,7 +3851,7 @@
         <v>730</v>
       </c>
       <c r="F16" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -3875,7 +3872,7 @@
         <v>723</v>
       </c>
       <c r="F17" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -3934,7 +3931,7 @@
         <v>730</v>
       </c>
       <c r="F20" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -4338,7 +4335,7 @@
         <v>730</v>
       </c>
       <c r="F40" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -4359,7 +4356,7 @@
         <v>723</v>
       </c>
       <c r="F41" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -4540,7 +4537,7 @@
         <v>730</v>
       </c>
       <c r="F50" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
@@ -4582,7 +4579,7 @@
         <v>730</v>
       </c>
       <c r="F52" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
@@ -4700,7 +4697,7 @@
         <v>730</v>
       </c>
       <c r="F58" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4742,7 +4739,7 @@
         <v>730</v>
       </c>
       <c r="F60" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
@@ -5253,7 +5250,7 @@
         <v>725</v>
       </c>
       <c r="F86" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
@@ -5295,7 +5292,7 @@
         <v>725</v>
       </c>
       <c r="F88" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
@@ -5337,7 +5334,7 @@
         <v>725</v>
       </c>
       <c r="F90" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
@@ -5379,7 +5376,7 @@
         <v>725</v>
       </c>
       <c r="F92" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
@@ -5421,7 +5418,7 @@
         <v>725</v>
       </c>
       <c r="F94" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
@@ -5463,7 +5460,7 @@
         <v>725</v>
       </c>
       <c r="F96" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
@@ -5505,7 +5502,7 @@
         <v>725</v>
       </c>
       <c r="F98" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
@@ -5547,7 +5544,7 @@
         <v>725</v>
       </c>
       <c r="F100" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
@@ -5589,7 +5586,7 @@
         <v>725</v>
       </c>
       <c r="F102" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
@@ -5631,7 +5628,7 @@
         <v>725</v>
       </c>
       <c r="F104" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
@@ -5673,7 +5670,7 @@
         <v>725</v>
       </c>
       <c r="F106" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
@@ -5715,7 +5712,7 @@
         <v>725</v>
       </c>
       <c r="F108" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
@@ -5757,7 +5754,7 @@
         <v>725</v>
       </c>
       <c r="F110" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
@@ -5799,7 +5796,7 @@
         <v>725</v>
       </c>
       <c r="F112" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
@@ -5841,7 +5838,7 @@
         <v>725</v>
       </c>
       <c r="F114" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
@@ -5883,7 +5880,7 @@
         <v>725</v>
       </c>
       <c r="F116" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
@@ -5925,7 +5922,7 @@
         <v>725</v>
       </c>
       <c r="F118" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
@@ -5967,7 +5964,7 @@
         <v>725</v>
       </c>
       <c r="F120" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
@@ -6009,7 +6006,7 @@
         <v>725</v>
       </c>
       <c r="F122" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
@@ -6051,7 +6048,7 @@
         <v>725</v>
       </c>
       <c r="F124" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
@@ -6093,7 +6090,7 @@
         <v>725</v>
       </c>
       <c r="F126" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -6135,7 +6132,7 @@
         <v>725</v>
       </c>
       <c r="F128" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -6177,7 +6174,7 @@
         <v>725</v>
       </c>
       <c r="F130" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
@@ -6219,7 +6216,7 @@
         <v>725</v>
       </c>
       <c r="F132" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
@@ -6261,7 +6258,7 @@
         <v>725</v>
       </c>
       <c r="F134" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
@@ -6303,7 +6300,7 @@
         <v>725</v>
       </c>
       <c r="F136" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
@@ -6345,7 +6342,7 @@
         <v>725</v>
       </c>
       <c r="F138" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
@@ -6387,7 +6384,7 @@
         <v>725</v>
       </c>
       <c r="F140" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
@@ -6429,7 +6426,7 @@
         <v>725</v>
       </c>
       <c r="F142" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.35">
@@ -6471,7 +6468,7 @@
         <v>725</v>
       </c>
       <c r="F144" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
@@ -6513,7 +6510,7 @@
         <v>725</v>
       </c>
       <c r="F146" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.35">
@@ -6555,7 +6552,7 @@
         <v>725</v>
       </c>
       <c r="F148" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.35">
@@ -6597,7 +6594,7 @@
         <v>725</v>
       </c>
       <c r="F150" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
@@ -6639,7 +6636,7 @@
         <v>725</v>
       </c>
       <c r="F152" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.35">
@@ -6681,7 +6678,7 @@
         <v>725</v>
       </c>
       <c r="F154" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.35">
@@ -6723,7 +6720,7 @@
         <v>725</v>
       </c>
       <c r="F156" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.35">
@@ -6765,7 +6762,7 @@
         <v>725</v>
       </c>
       <c r="F158" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.35">
@@ -6807,7 +6804,7 @@
         <v>725</v>
       </c>
       <c r="F160" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.35">
@@ -6849,7 +6846,7 @@
         <v>725</v>
       </c>
       <c r="F162" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.35">
@@ -6891,7 +6888,7 @@
         <v>725</v>
       </c>
       <c r="F164" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.35">
@@ -6933,7 +6930,7 @@
         <v>725</v>
       </c>
       <c r="F166" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.35">
@@ -6975,7 +6972,7 @@
         <v>725</v>
       </c>
       <c r="F168" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.35">
@@ -7017,7 +7014,7 @@
         <v>725</v>
       </c>
       <c r="F170" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.35">
@@ -7059,7 +7056,7 @@
         <v>725</v>
       </c>
       <c r="F172" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.35">
@@ -7101,7 +7098,7 @@
         <v>725</v>
       </c>
       <c r="F174" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.35">
@@ -7143,7 +7140,7 @@
         <v>725</v>
       </c>
       <c r="F176" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.35">
@@ -7185,7 +7182,7 @@
         <v>725</v>
       </c>
       <c r="F178" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.35">
@@ -7227,7 +7224,7 @@
         <v>725</v>
       </c>
       <c r="F180" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.35">
@@ -7269,7 +7266,7 @@
         <v>725</v>
       </c>
       <c r="F182" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.35">
@@ -7311,7 +7308,7 @@
         <v>725</v>
       </c>
       <c r="F184" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.35">
@@ -7353,7 +7350,7 @@
         <v>725</v>
       </c>
       <c r="F186" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.35">
@@ -7395,7 +7392,7 @@
         <v>725</v>
       </c>
       <c r="F188" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.35">
@@ -7416,7 +7413,7 @@
         <v>730</v>
       </c>
       <c r="F189" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.35">
@@ -7455,7 +7452,7 @@
         <v>730</v>
       </c>
       <c r="F191" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.35">
@@ -7650,7 +7647,7 @@
         <v>723</v>
       </c>
       <c r="F201" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.35">
@@ -7692,7 +7689,7 @@
         <v>723</v>
       </c>
       <c r="F203" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.35">
@@ -9107,7 +9104,7 @@
         <v>730</v>
       </c>
       <c r="F275" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.35">
@@ -9146,7 +9143,7 @@
         <v>730</v>
       </c>
       <c r="F277" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.35">
@@ -9185,7 +9182,7 @@
         <v>730</v>
       </c>
       <c r="F279" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.35">
@@ -9223,7 +9220,7 @@
         <v>730</v>
       </c>
       <c r="F281" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.35">
@@ -9245,7 +9242,7 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B283" t="s">
         <v>718</v>
@@ -9261,12 +9258,12 @@
         <v>732</v>
       </c>
       <c r="F283" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B284" t="s">
         <v>719</v>
@@ -9283,7 +9280,7 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B285" t="s">
         <v>718</v>
@@ -9299,12 +9296,12 @@
         <v>732</v>
       </c>
       <c r="F285" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B286" t="s">
         <v>719</v>
@@ -9337,7 +9334,7 @@
         <v>732</v>
       </c>
       <c r="F287" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.35">
@@ -9375,7 +9372,7 @@
         <v>732</v>
       </c>
       <c r="F289" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.35">
@@ -9413,7 +9410,7 @@
         <v>730</v>
       </c>
       <c r="F291" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.35">
@@ -9434,7 +9431,7 @@
         <v>723</v>
       </c>
       <c r="F292" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.35">
@@ -9455,7 +9452,7 @@
         <v>730</v>
       </c>
       <c r="F293" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.35">
@@ -9497,7 +9494,7 @@
         <v>730</v>
       </c>
       <c r="F295" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.35">
@@ -9518,7 +9515,7 @@
         <v>723</v>
       </c>
       <c r="F296" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.35">
@@ -9539,7 +9536,7 @@
         <v>731</v>
       </c>
       <c r="F297" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.35">
@@ -9612,7 +9609,7 @@
         <v>731</v>
       </c>
       <c r="F301" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.35">
@@ -9685,7 +9682,7 @@
         <v>730</v>
       </c>
       <c r="F305" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.35">
@@ -9706,7 +9703,7 @@
         <v>723</v>
       </c>
       <c r="F306" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.35">
@@ -9727,7 +9724,7 @@
         <v>730</v>
       </c>
       <c r="F307" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.35">
@@ -9766,7 +9763,7 @@
         <v>730</v>
       </c>
       <c r="F309" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.35">
@@ -9843,7 +9840,7 @@
         <v>730</v>
       </c>
       <c r="F313" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.35">
@@ -9882,7 +9879,7 @@
         <v>730</v>
       </c>
       <c r="F315" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.35">
@@ -9903,7 +9900,7 @@
         <v>723</v>
       </c>
       <c r="F316" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.35">
@@ -9975,7 +9972,7 @@
         <v>730</v>
       </c>
       <c r="F320" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.35">
@@ -10052,7 +10049,7 @@
         <v>722</v>
       </c>
       <c r="F324" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.35">
@@ -10073,7 +10070,7 @@
         <v>730</v>
       </c>
       <c r="F325" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.35">
@@ -10129,7 +10126,7 @@
         <v>722</v>
       </c>
       <c r="F328" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.35">
@@ -10150,7 +10147,7 @@
         <v>730</v>
       </c>
       <c r="F329" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.35">
@@ -10188,7 +10185,7 @@
         <v>730</v>
       </c>
       <c r="F331" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.35">
@@ -10248,7 +10245,7 @@
         <v>730</v>
       </c>
       <c r="F334" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.35">
@@ -10325,7 +10322,7 @@
         <v>730</v>
       </c>
       <c r="F338" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.35">
@@ -10480,7 +10477,7 @@
         <v>730</v>
       </c>
       <c r="F346" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.35">
@@ -10553,7 +10550,7 @@
         <v>730</v>
       </c>
       <c r="F350" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.35">
@@ -10574,7 +10571,7 @@
         <v>723</v>
       </c>
       <c r="F351" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.35">
@@ -10646,7 +10643,7 @@
         <v>730</v>
       </c>
       <c r="F355" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.35">
@@ -10706,7 +10703,7 @@
         <v>730</v>
       </c>
       <c r="F358" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.35">
@@ -10806,7 +10803,7 @@
         <v>730</v>
       </c>
       <c r="F363" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.35">
@@ -10827,7 +10824,7 @@
         <v>723</v>
       </c>
       <c r="F364" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.35">
@@ -10882,7 +10879,7 @@
         <v>722</v>
       </c>
       <c r="F367" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.35">
@@ -10903,7 +10900,7 @@
         <v>730</v>
       </c>
       <c r="F368" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.35">
@@ -10942,7 +10939,7 @@
         <v>730</v>
       </c>
       <c r="F370" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.35">
@@ -10981,7 +10978,7 @@
         <v>730</v>
       </c>
       <c r="F372" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.35">
@@ -11023,7 +11020,7 @@
         <v>723</v>
       </c>
       <c r="F374" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.35">
@@ -11078,7 +11075,7 @@
         <v>730</v>
       </c>
       <c r="F377" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.35">
@@ -11218,7 +11215,7 @@
         <v>723</v>
       </c>
       <c r="F384" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.35">
@@ -11302,7 +11299,7 @@
         <v>723</v>
       </c>
       <c r="F388" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.35">
@@ -11601,7 +11598,7 @@
         <v>723</v>
       </c>
       <c r="F403" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.35">
@@ -11622,7 +11619,7 @@
         <v>730</v>
       </c>
       <c r="F404" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.35">
@@ -11702,7 +11699,7 @@
         <v>730</v>
       </c>
       <c r="F408" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.35">
@@ -11803,7 +11800,7 @@
         <v>723</v>
       </c>
       <c r="F413" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.35">
@@ -11824,7 +11821,7 @@
         <v>730</v>
       </c>
       <c r="F414" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.35">
@@ -11862,7 +11859,7 @@
         <v>730</v>
       </c>
       <c r="F416" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.35">
@@ -11901,7 +11898,7 @@
         <v>730</v>
       </c>
       <c r="F418" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.35">
@@ -11943,7 +11940,7 @@
         <v>730</v>
       </c>
       <c r="F420" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.35">
@@ -11985,7 +11982,7 @@
         <v>730</v>
       </c>
       <c r="F422" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.35">
@@ -12069,7 +12066,7 @@
         <v>730</v>
       </c>
       <c r="F426" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.35">
@@ -12132,7 +12129,7 @@
         <v>730</v>
       </c>
       <c r="F429" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.35">
@@ -12195,7 +12192,7 @@
         <v>730</v>
       </c>
       <c r="F432" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.35">
@@ -12300,7 +12297,7 @@
         <v>730</v>
       </c>
       <c r="F437" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.35">
@@ -12339,7 +12336,7 @@
         <v>730</v>
       </c>
       <c r="F439" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.35">
@@ -12417,7 +12414,7 @@
         <v>730</v>
       </c>
       <c r="F443" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.35">
@@ -12438,7 +12435,7 @@
         <v>730</v>
       </c>
       <c r="F444" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.35">
@@ -12477,7 +12474,7 @@
         <v>730</v>
       </c>
       <c r="F446" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.35">
@@ -12498,7 +12495,7 @@
         <v>723</v>
       </c>
       <c r="F447" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.35">
@@ -12519,7 +12516,7 @@
         <v>730</v>
       </c>
       <c r="F448" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.35">
@@ -12561,7 +12558,7 @@
         <v>722</v>
       </c>
       <c r="F450" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.35">
@@ -12599,7 +12596,7 @@
         <v>730</v>
       </c>
       <c r="F452" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.35">
@@ -12638,7 +12635,7 @@
         <v>730</v>
       </c>
       <c r="F454" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.35">
@@ -12677,7 +12674,7 @@
         <v>730</v>
       </c>
       <c r="F456" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.35">
@@ -12716,7 +12713,7 @@
         <v>730</v>
       </c>
       <c r="F458" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.35">
@@ -12793,7 +12790,7 @@
         <v>730</v>
       </c>
       <c r="F462" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.35">
@@ -12832,7 +12829,7 @@
         <v>730</v>
       </c>
       <c r="F464" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.35">
@@ -12871,7 +12868,7 @@
         <v>730</v>
       </c>
       <c r="F466" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.35">
@@ -12910,7 +12907,7 @@
         <v>730</v>
       </c>
       <c r="F468" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.35">
@@ -12931,7 +12928,7 @@
         <v>723</v>
       </c>
       <c r="F469" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.35">
@@ -13003,7 +13000,7 @@
         <v>730</v>
       </c>
       <c r="F473" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.35">
@@ -13042,7 +13039,7 @@
         <v>730</v>
       </c>
       <c r="F475" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.35">
@@ -13163,7 +13160,7 @@
         <v>730</v>
       </c>
       <c r="F481" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.35">
@@ -13184,7 +13181,7 @@
         <v>723</v>
       </c>
       <c r="F482" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.35">
@@ -13256,7 +13253,7 @@
         <v>730</v>
       </c>
       <c r="F486" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.35">
@@ -13294,7 +13291,7 @@
         <v>730</v>
       </c>
       <c r="F488" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.35">
@@ -13375,7 +13372,7 @@
         <v>729</v>
       </c>
       <c r="F492" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.35">
@@ -13417,7 +13414,7 @@
         <v>729</v>
       </c>
       <c r="F494" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.35">
@@ -13459,7 +13456,7 @@
         <v>729</v>
       </c>
       <c r="F496" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.35">
@@ -13501,7 +13498,7 @@
         <v>729</v>
       </c>
       <c r="F498" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.35">
@@ -13543,7 +13540,7 @@
         <v>729</v>
       </c>
       <c r="F500" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.35">
@@ -13585,7 +13582,7 @@
         <v>729</v>
       </c>
       <c r="F502" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.35">
@@ -13627,7 +13624,7 @@
         <v>729</v>
       </c>
       <c r="F504" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.35">
@@ -13669,7 +13666,7 @@
         <v>729</v>
       </c>
       <c r="F506" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.35">
@@ -13711,7 +13708,7 @@
         <v>729</v>
       </c>
       <c r="F508" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.35">
@@ -13753,7 +13750,7 @@
         <v>729</v>
       </c>
       <c r="F510" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.35">
@@ -13795,7 +13792,7 @@
         <v>729</v>
       </c>
       <c r="F512" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.35">
@@ -13837,7 +13834,7 @@
         <v>729</v>
       </c>
       <c r="F514" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.35">
@@ -13879,7 +13876,7 @@
         <v>729</v>
       </c>
       <c r="F516" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.35">
@@ -13921,7 +13918,7 @@
         <v>729</v>
       </c>
       <c r="F518" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.35">
@@ -13963,7 +13960,7 @@
         <v>729</v>
       </c>
       <c r="F520" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.35">
@@ -14005,7 +14002,7 @@
         <v>729</v>
       </c>
       <c r="F522" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.35">
@@ -14047,7 +14044,7 @@
         <v>729</v>
       </c>
       <c r="F524" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.35">
@@ -14089,7 +14086,7 @@
         <v>729</v>
       </c>
       <c r="F526" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.35">
@@ -14152,7 +14149,7 @@
         <v>730</v>
       </c>
       <c r="F529" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.35">
@@ -14194,7 +14191,7 @@
         <v>723</v>
       </c>
       <c r="F531" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.35">
@@ -14215,7 +14212,7 @@
         <v>730</v>
       </c>
       <c r="F532" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.35">
@@ -14278,7 +14275,7 @@
         <v>723</v>
       </c>
       <c r="F535" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.35">
@@ -14425,7 +14422,7 @@
         <v>723</v>
       </c>
       <c r="F542" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.35">
@@ -14467,7 +14464,7 @@
         <v>723</v>
       </c>
       <c r="F544" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.35">
@@ -14506,7 +14503,7 @@
         <v>730</v>
       </c>
       <c r="F546" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.35">
@@ -14527,7 +14524,7 @@
         <v>730</v>
       </c>
       <c r="F547" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.35">
@@ -14566,7 +14563,7 @@
         <v>730</v>
       </c>
       <c r="F549" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.35">
@@ -14605,7 +14602,7 @@
         <v>730</v>
       </c>
       <c r="F551" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.35">
@@ -14647,7 +14644,7 @@
         <v>730</v>
       </c>
       <c r="F553" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.35">
@@ -14689,7 +14686,7 @@
         <v>730</v>
       </c>
       <c r="F555" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.35">
@@ -14773,7 +14770,7 @@
         <v>730</v>
       </c>
       <c r="F559" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.35">
@@ -14836,7 +14833,7 @@
         <v>730</v>
       </c>
       <c r="F562" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.35">
@@ -14899,7 +14896,7 @@
         <v>730</v>
       </c>
       <c r="F565" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.35">
@@ -15004,7 +15001,7 @@
         <v>730</v>
       </c>
       <c r="F570" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.35">
@@ -15046,7 +15043,7 @@
         <v>730</v>
       </c>
       <c r="F572" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.35">
@@ -15188,7 +15185,7 @@
         <v>730</v>
       </c>
       <c r="F579" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.35">
@@ -15226,7 +15223,7 @@
         <v>730</v>
       </c>
       <c r="F581" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.35">
@@ -15247,7 +15244,7 @@
         <v>723</v>
       </c>
       <c r="F582" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.35">
@@ -15268,7 +15265,7 @@
         <v>730</v>
       </c>
       <c r="F583" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.35">
@@ -15289,7 +15286,7 @@
         <v>723</v>
       </c>
       <c r="F584" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.35">
@@ -15310,7 +15307,7 @@
         <v>730</v>
       </c>
       <c r="F585" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.35">
@@ -15481,7 +15478,7 @@
         <v>730</v>
       </c>
       <c r="F594" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.35">
@@ -15519,7 +15516,7 @@
         <v>730</v>
       </c>
       <c r="F596" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.35">
@@ -15923,7 +15920,7 @@
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B618" t="s">
         <v>718</v>
@@ -15939,12 +15936,12 @@
         <v>730</v>
       </c>
       <c r="F618" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B619" t="s">
         <v>719</v>
@@ -15962,7 +15959,7 @@
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B620" t="s">
         <v>718</v>
@@ -15978,12 +15975,12 @@
         <v>730</v>
       </c>
       <c r="F620" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B621" t="s">
         <v>719</v>
@@ -16093,7 +16090,7 @@
         <v>723</v>
       </c>
       <c r="F626" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.35">
@@ -16465,7 +16462,7 @@
         <v>733</v>
       </c>
       <c r="F645" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.35">
@@ -16486,7 +16483,7 @@
         <v>729</v>
       </c>
       <c r="F646" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.35">
@@ -16507,7 +16504,7 @@
         <v>733</v>
       </c>
       <c r="F647" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.35">
@@ -16528,7 +16525,7 @@
         <v>729</v>
       </c>
       <c r="F648" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.35">
@@ -16549,7 +16546,7 @@
         <v>733</v>
       </c>
       <c r="F649" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.35">
@@ -16570,7 +16567,7 @@
         <v>729</v>
       </c>
       <c r="F650" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.35">
@@ -16591,7 +16588,7 @@
         <v>733</v>
       </c>
       <c r="F651" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.35">
@@ -16612,7 +16609,7 @@
         <v>729</v>
       </c>
       <c r="F652" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.35">
@@ -16633,7 +16630,7 @@
         <v>733</v>
       </c>
       <c r="F653" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.35">
@@ -16654,7 +16651,7 @@
         <v>729</v>
       </c>
       <c r="F654" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.35">
@@ -16675,7 +16672,7 @@
         <v>733</v>
       </c>
       <c r="F655" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.35">
@@ -16696,7 +16693,7 @@
         <v>729</v>
       </c>
       <c r="F656" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.35">
@@ -16717,7 +16714,7 @@
         <v>733</v>
       </c>
       <c r="F657" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.35">
@@ -16738,7 +16735,7 @@
         <v>729</v>
       </c>
       <c r="F658" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.35">
@@ -16759,7 +16756,7 @@
         <v>733</v>
       </c>
       <c r="F659" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.35">
@@ -16780,7 +16777,7 @@
         <v>729</v>
       </c>
       <c r="F660" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.35">
@@ -16801,7 +16798,7 @@
         <v>733</v>
       </c>
       <c r="F661" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.35">
@@ -16839,7 +16836,7 @@
         <v>733</v>
       </c>
       <c r="F663" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.35">
@@ -16877,7 +16874,7 @@
         <v>733</v>
       </c>
       <c r="F665" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.35">
@@ -16898,7 +16895,7 @@
         <v>729</v>
       </c>
       <c r="F666" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.35">
@@ -16919,7 +16916,7 @@
         <v>733</v>
       </c>
       <c r="F667" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.35">
@@ -16940,7 +16937,7 @@
         <v>729</v>
       </c>
       <c r="F668" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.35">
@@ -16961,7 +16958,7 @@
         <v>733</v>
       </c>
       <c r="F669" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.35">
@@ -16982,7 +16979,7 @@
         <v>729</v>
       </c>
       <c r="F670" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.35">
@@ -17003,7 +17000,7 @@
         <v>733</v>
       </c>
       <c r="F671" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.35">
@@ -17024,7 +17021,7 @@
         <v>729</v>
       </c>
       <c r="F672" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.35">
@@ -17045,7 +17042,7 @@
         <v>733</v>
       </c>
       <c r="F673" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.35">
@@ -17066,7 +17063,7 @@
         <v>729</v>
       </c>
       <c r="F674" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.35">
@@ -17087,7 +17084,7 @@
         <v>733</v>
       </c>
       <c r="F675" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.35">
@@ -17108,7 +17105,7 @@
         <v>729</v>
       </c>
       <c r="F676" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.35">
@@ -17150,7 +17147,7 @@
         <v>729</v>
       </c>
       <c r="F678" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.35">
@@ -17192,7 +17189,7 @@
         <v>729</v>
       </c>
       <c r="F680" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.35">
@@ -17234,7 +17231,7 @@
         <v>729</v>
       </c>
       <c r="F682" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.35">
@@ -17276,7 +17273,7 @@
         <v>729</v>
       </c>
       <c r="F684" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.35">
@@ -17318,7 +17315,7 @@
         <v>729</v>
       </c>
       <c r="F686" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.35">
@@ -17360,7 +17357,7 @@
         <v>729</v>
       </c>
       <c r="F688" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.35">
@@ -17402,7 +17399,7 @@
         <v>729</v>
       </c>
       <c r="F690" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.35">
@@ -17444,7 +17441,7 @@
         <v>729</v>
       </c>
       <c r="F692" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.35">
@@ -17705,7 +17702,7 @@
         <v>730</v>
       </c>
       <c r="F705" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.35">
@@ -18041,7 +18038,7 @@
         <v>725</v>
       </c>
       <c r="F723" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="724" spans="1:6" x14ac:dyDescent="0.35">
@@ -18083,7 +18080,7 @@
         <v>725</v>
       </c>
       <c r="F725" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="726" spans="1:6" x14ac:dyDescent="0.35">
@@ -18125,7 +18122,7 @@
         <v>725</v>
       </c>
       <c r="F727" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="728" spans="1:6" x14ac:dyDescent="0.35">
@@ -18167,7 +18164,7 @@
         <v>725</v>
       </c>
       <c r="F729" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.35">
@@ -18209,7 +18206,7 @@
         <v>725</v>
       </c>
       <c r="F731" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="732" spans="1:6" x14ac:dyDescent="0.35">
@@ -18251,7 +18248,7 @@
         <v>725</v>
       </c>
       <c r="F733" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="734" spans="1:6" x14ac:dyDescent="0.35">
@@ -18293,7 +18290,7 @@
         <v>725</v>
       </c>
       <c r="F735" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="736" spans="1:6" x14ac:dyDescent="0.35">
@@ -18335,7 +18332,7 @@
         <v>725</v>
       </c>
       <c r="F737" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="738" spans="1:6" x14ac:dyDescent="0.35">
@@ -18377,7 +18374,7 @@
         <v>725</v>
       </c>
       <c r="F739" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="740" spans="1:6" x14ac:dyDescent="0.35">
@@ -18419,7 +18416,7 @@
         <v>725</v>
       </c>
       <c r="F741" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="742" spans="1:6" x14ac:dyDescent="0.35">
@@ -18461,7 +18458,7 @@
         <v>725</v>
       </c>
       <c r="F743" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.35">
@@ -18503,7 +18500,7 @@
         <v>725</v>
       </c>
       <c r="F745" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.35">
@@ -18545,7 +18542,7 @@
         <v>725</v>
       </c>
       <c r="F747" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="748" spans="1:6" x14ac:dyDescent="0.35">
@@ -18587,7 +18584,7 @@
         <v>725</v>
       </c>
       <c r="F749" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="750" spans="1:6" x14ac:dyDescent="0.35">
@@ -18629,7 +18626,7 @@
         <v>725</v>
       </c>
       <c r="F751" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.35">
@@ -18671,7 +18668,7 @@
         <v>725</v>
       </c>
       <c r="F753" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="754" spans="1:6" x14ac:dyDescent="0.35">
@@ -18713,7 +18710,7 @@
         <v>725</v>
       </c>
       <c r="F755" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.35">
@@ -18755,7 +18752,7 @@
         <v>725</v>
       </c>
       <c r="F757" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.35">
@@ -18797,7 +18794,7 @@
         <v>725</v>
       </c>
       <c r="F759" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="760" spans="1:6" x14ac:dyDescent="0.35">
@@ -18839,7 +18836,7 @@
         <v>725</v>
       </c>
       <c r="F761" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="762" spans="1:6" x14ac:dyDescent="0.35">
@@ -18881,7 +18878,7 @@
         <v>725</v>
       </c>
       <c r="F763" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="764" spans="1:6" x14ac:dyDescent="0.35">
@@ -18923,7 +18920,7 @@
         <v>725</v>
       </c>
       <c r="F765" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="766" spans="1:6" x14ac:dyDescent="0.35">
@@ -18965,7 +18962,7 @@
         <v>725</v>
       </c>
       <c r="F767" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="768" spans="1:6" x14ac:dyDescent="0.35">
@@ -19007,7 +19004,7 @@
         <v>725</v>
       </c>
       <c r="F769" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="770" spans="1:6" x14ac:dyDescent="0.35">
@@ -19049,7 +19046,7 @@
         <v>725</v>
       </c>
       <c r="F771" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="772" spans="1:6" x14ac:dyDescent="0.35">
@@ -19091,7 +19088,7 @@
         <v>725</v>
       </c>
       <c r="F773" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.35">
@@ -19133,7 +19130,7 @@
         <v>725</v>
       </c>
       <c r="F775" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="776" spans="1:6" x14ac:dyDescent="0.35">
@@ -19175,7 +19172,7 @@
         <v>725</v>
       </c>
       <c r="F777" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="778" spans="1:6" x14ac:dyDescent="0.35">
@@ -19217,7 +19214,7 @@
         <v>725</v>
       </c>
       <c r="F779" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="780" spans="1:6" x14ac:dyDescent="0.35">
@@ -19259,7 +19256,7 @@
         <v>725</v>
       </c>
       <c r="F781" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="782" spans="1:6" x14ac:dyDescent="0.35">
@@ -19301,7 +19298,7 @@
         <v>725</v>
       </c>
       <c r="F783" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="784" spans="1:6" x14ac:dyDescent="0.35">
@@ -19343,7 +19340,7 @@
         <v>725</v>
       </c>
       <c r="F785" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="786" spans="1:6" x14ac:dyDescent="0.35">
@@ -19385,7 +19382,7 @@
         <v>725</v>
       </c>
       <c r="F787" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="788" spans="1:6" x14ac:dyDescent="0.35">
@@ -19427,7 +19424,7 @@
         <v>725</v>
       </c>
       <c r="F789" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="790" spans="1:6" x14ac:dyDescent="0.35">
@@ -19469,7 +19466,7 @@
         <v>725</v>
       </c>
       <c r="F791" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="792" spans="1:6" x14ac:dyDescent="0.35">
@@ -19511,7 +19508,7 @@
         <v>725</v>
       </c>
       <c r="F793" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="794" spans="1:6" x14ac:dyDescent="0.35">
@@ -19553,7 +19550,7 @@
         <v>725</v>
       </c>
       <c r="F795" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="796" spans="1:6" x14ac:dyDescent="0.35">
@@ -19595,7 +19592,7 @@
         <v>725</v>
       </c>
       <c r="F797" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="798" spans="1:6" x14ac:dyDescent="0.35">
@@ -19637,7 +19634,7 @@
         <v>725</v>
       </c>
       <c r="F799" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="800" spans="1:6" x14ac:dyDescent="0.35">
@@ -19679,7 +19676,7 @@
         <v>725</v>
       </c>
       <c r="F801" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="802" spans="1:6" x14ac:dyDescent="0.35">
@@ -19721,7 +19718,7 @@
         <v>725</v>
       </c>
       <c r="F803" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="804" spans="1:6" x14ac:dyDescent="0.35">
@@ -19763,7 +19760,7 @@
         <v>725</v>
       </c>
       <c r="F805" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="806" spans="1:6" x14ac:dyDescent="0.35">
@@ -19805,7 +19802,7 @@
         <v>725</v>
       </c>
       <c r="F807" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="808" spans="1:6" x14ac:dyDescent="0.35">
@@ -19847,7 +19844,7 @@
         <v>725</v>
       </c>
       <c r="F809" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="810" spans="1:6" x14ac:dyDescent="0.35">
@@ -19889,7 +19886,7 @@
         <v>725</v>
       </c>
       <c r="F811" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="812" spans="1:6" x14ac:dyDescent="0.35">
@@ -19931,7 +19928,7 @@
         <v>725</v>
       </c>
       <c r="F813" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="814" spans="1:6" x14ac:dyDescent="0.35">
@@ -19973,7 +19970,7 @@
         <v>725</v>
       </c>
       <c r="F815" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="816" spans="1:6" x14ac:dyDescent="0.35">
@@ -20015,7 +20012,7 @@
         <v>725</v>
       </c>
       <c r="F817" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="818" spans="1:6" x14ac:dyDescent="0.35">
@@ -20354,7 +20351,7 @@
         <v>733</v>
       </c>
       <c r="F835" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="836" spans="1:6" x14ac:dyDescent="0.35">
@@ -20391,7 +20388,7 @@
         <v>722</v>
       </c>
       <c r="F837" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="838" spans="1:6" x14ac:dyDescent="0.35">
@@ -20411,7 +20408,7 @@
         <v>722</v>
       </c>
       <c r="F838" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="839" spans="1:6" x14ac:dyDescent="0.35">
@@ -20432,7 +20429,7 @@
         <v>733</v>
       </c>
       <c r="F839" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="840" spans="1:6" x14ac:dyDescent="0.35">
@@ -20469,7 +20466,7 @@
         <v>722</v>
       </c>
       <c r="F841" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="842" spans="1:6" x14ac:dyDescent="0.35">
@@ -20489,7 +20486,7 @@
         <v>722</v>
       </c>
       <c r="F842" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="843" spans="1:6" x14ac:dyDescent="0.35">
@@ -20510,7 +20507,7 @@
         <v>733</v>
       </c>
       <c r="F843" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="844" spans="1:6" x14ac:dyDescent="0.35">
@@ -20547,7 +20544,7 @@
         <v>722</v>
       </c>
       <c r="F845" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="846" spans="1:6" x14ac:dyDescent="0.35">
@@ -20567,7 +20564,7 @@
         <v>722</v>
       </c>
       <c r="F846" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="847" spans="1:6" x14ac:dyDescent="0.35">
@@ -20588,7 +20585,7 @@
         <v>733</v>
       </c>
       <c r="F847" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="848" spans="1:6" x14ac:dyDescent="0.35">
@@ -20625,7 +20622,7 @@
         <v>722</v>
       </c>
       <c r="F849" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="850" spans="1:6" x14ac:dyDescent="0.35">
@@ -20645,7 +20642,7 @@
         <v>722</v>
       </c>
       <c r="F850" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="851" spans="1:6" x14ac:dyDescent="0.35">
@@ -20666,7 +20663,7 @@
         <v>733</v>
       </c>
       <c r="F851" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="852" spans="1:6" x14ac:dyDescent="0.35">
@@ -20703,7 +20700,7 @@
         <v>722</v>
       </c>
       <c r="F853" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="854" spans="1:6" x14ac:dyDescent="0.35">
@@ -20723,7 +20720,7 @@
         <v>722</v>
       </c>
       <c r="F854" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="855" spans="1:6" x14ac:dyDescent="0.35">
@@ -20744,7 +20741,7 @@
         <v>733</v>
       </c>
       <c r="F855" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="856" spans="1:6" x14ac:dyDescent="0.35">
@@ -20782,7 +20779,7 @@
         <v>722</v>
       </c>
       <c r="F857" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="858" spans="1:6" x14ac:dyDescent="0.35">
@@ -20802,7 +20799,7 @@
         <v>722</v>
       </c>
       <c r="F858" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="859" spans="1:6" x14ac:dyDescent="0.35">
@@ -20823,7 +20820,7 @@
         <v>733</v>
       </c>
       <c r="F859" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="860" spans="1:6" x14ac:dyDescent="0.35">
@@ -20861,7 +20858,7 @@
         <v>722</v>
       </c>
       <c r="F861" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="862" spans="1:6" x14ac:dyDescent="0.35">
@@ -20881,7 +20878,7 @@
         <v>722</v>
       </c>
       <c r="F862" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="863" spans="1:6" x14ac:dyDescent="0.35">
@@ -20902,7 +20899,7 @@
         <v>733</v>
       </c>
       <c r="F863" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="864" spans="1:6" x14ac:dyDescent="0.35">
@@ -20939,7 +20936,7 @@
         <v>722</v>
       </c>
       <c r="F865" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="866" spans="1:6" x14ac:dyDescent="0.35">
@@ -20959,7 +20956,7 @@
         <v>722</v>
       </c>
       <c r="F866" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="867" spans="1:6" x14ac:dyDescent="0.35">
@@ -20980,7 +20977,7 @@
         <v>733</v>
       </c>
       <c r="F867" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="868" spans="1:6" x14ac:dyDescent="0.35">
@@ -21017,7 +21014,7 @@
         <v>722</v>
       </c>
       <c r="F869" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="870" spans="1:6" x14ac:dyDescent="0.35">
@@ -21037,7 +21034,7 @@
         <v>722</v>
       </c>
       <c r="F870" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="871" spans="1:6" x14ac:dyDescent="0.35">
@@ -21058,7 +21055,7 @@
         <v>733</v>
       </c>
       <c r="F871" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="872" spans="1:6" x14ac:dyDescent="0.35">
@@ -21095,7 +21092,7 @@
         <v>722</v>
       </c>
       <c r="F873" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="874" spans="1:6" x14ac:dyDescent="0.35">
@@ -21115,7 +21112,7 @@
         <v>722</v>
       </c>
       <c r="F874" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="875" spans="1:6" x14ac:dyDescent="0.35">
@@ -21292,7 +21289,7 @@
         <v>732</v>
       </c>
       <c r="F883" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="884" spans="1:6" x14ac:dyDescent="0.35">
@@ -21331,7 +21328,7 @@
         <v>733</v>
       </c>
       <c r="F885" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="886" spans="1:6" x14ac:dyDescent="0.35">
@@ -21352,7 +21349,7 @@
         <v>729</v>
       </c>
       <c r="F886" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="887" spans="1:6" x14ac:dyDescent="0.35">
@@ -21373,7 +21370,7 @@
         <v>733</v>
       </c>
       <c r="F887" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="888" spans="1:6" x14ac:dyDescent="0.35">
@@ -21394,7 +21391,7 @@
         <v>729</v>
       </c>
       <c r="F888" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="889" spans="1:6" x14ac:dyDescent="0.35">
@@ -21415,7 +21412,7 @@
         <v>733</v>
       </c>
       <c r="F889" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="890" spans="1:6" x14ac:dyDescent="0.35">
@@ -21436,7 +21433,7 @@
         <v>729</v>
       </c>
       <c r="F890" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="891" spans="1:6" x14ac:dyDescent="0.35">
@@ -21457,7 +21454,7 @@
         <v>733</v>
       </c>
       <c r="F891" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="892" spans="1:6" x14ac:dyDescent="0.35">
@@ -21478,7 +21475,7 @@
         <v>729</v>
       </c>
       <c r="F892" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="893" spans="1:6" x14ac:dyDescent="0.35">
@@ -21499,7 +21496,7 @@
         <v>733</v>
       </c>
       <c r="F893" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="894" spans="1:6" x14ac:dyDescent="0.35">
@@ -21537,7 +21534,7 @@
         <v>733</v>
       </c>
       <c r="F895" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="896" spans="1:6" x14ac:dyDescent="0.35">
@@ -21558,7 +21555,7 @@
         <v>729</v>
       </c>
       <c r="F896" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="897" spans="1:6" x14ac:dyDescent="0.35">
@@ -21579,7 +21576,7 @@
         <v>733</v>
       </c>
       <c r="F897" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="898" spans="1:6" x14ac:dyDescent="0.35">
@@ -21600,7 +21597,7 @@
         <v>729</v>
       </c>
       <c r="F898" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="899" spans="1:6" x14ac:dyDescent="0.35">
@@ -21621,7 +21618,7 @@
         <v>733</v>
       </c>
       <c r="F899" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="900" spans="1:6" x14ac:dyDescent="0.35">
@@ -21642,7 +21639,7 @@
         <v>729</v>
       </c>
       <c r="F900" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="901" spans="1:6" x14ac:dyDescent="0.35">
@@ -21684,7 +21681,7 @@
         <v>729</v>
       </c>
       <c r="F902" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="903" spans="1:6" x14ac:dyDescent="0.35">
@@ -21726,7 +21723,7 @@
         <v>729</v>
       </c>
       <c r="F904" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="905" spans="1:6" x14ac:dyDescent="0.35">
@@ -21768,7 +21765,7 @@
         <v>729</v>
       </c>
       <c r="F906" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="907" spans="1:6" x14ac:dyDescent="0.35">
@@ -21810,7 +21807,7 @@
         <v>729</v>
       </c>
       <c r="F908" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="909" spans="1:6" x14ac:dyDescent="0.35">
@@ -21852,7 +21849,7 @@
         <v>729</v>
       </c>
       <c r="F910" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="911" spans="1:6" x14ac:dyDescent="0.35">
@@ -21894,7 +21891,7 @@
         <v>729</v>
       </c>
       <c r="F912" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="913" spans="1:6" x14ac:dyDescent="0.35">
@@ -21936,7 +21933,7 @@
         <v>729</v>
       </c>
       <c r="F914" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="915" spans="1:6" x14ac:dyDescent="0.35">
@@ -21978,7 +21975,7 @@
         <v>729</v>
       </c>
       <c r="F916" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="917" spans="1:6" x14ac:dyDescent="0.35">
@@ -22020,7 +22017,7 @@
         <v>729</v>
       </c>
       <c r="F918" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="919" spans="1:6" x14ac:dyDescent="0.35">
@@ -22062,7 +22059,7 @@
         <v>729</v>
       </c>
       <c r="F920" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="921" spans="1:6" x14ac:dyDescent="0.35">
@@ -22104,7 +22101,7 @@
         <v>729</v>
       </c>
       <c r="F922" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="923" spans="1:6" x14ac:dyDescent="0.35">
@@ -22146,7 +22143,7 @@
         <v>729</v>
       </c>
       <c r="F924" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="925" spans="1:6" x14ac:dyDescent="0.35">
@@ -22188,7 +22185,7 @@
         <v>729</v>
       </c>
       <c r="F926" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="927" spans="1:6" x14ac:dyDescent="0.35">
@@ -22230,7 +22227,7 @@
         <v>729</v>
       </c>
       <c r="F928" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="929" spans="1:6" x14ac:dyDescent="0.35">
@@ -22272,7 +22269,7 @@
         <v>729</v>
       </c>
       <c r="F930" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="931" spans="1:6" x14ac:dyDescent="0.35">
@@ -22314,7 +22311,7 @@
         <v>729</v>
       </c>
       <c r="F932" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="933" spans="1:6" x14ac:dyDescent="0.35">
@@ -22437,7 +22434,7 @@
         <v>723</v>
       </c>
       <c r="F938" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="939" spans="1:6" x14ac:dyDescent="0.35">
@@ -22458,7 +22455,7 @@
         <v>730</v>
       </c>
       <c r="F939" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="940" spans="1:6" x14ac:dyDescent="0.35">
@@ -22531,7 +22528,7 @@
         <v>730</v>
       </c>
       <c r="F943" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="944" spans="1:6" x14ac:dyDescent="0.35">
@@ -22588,7 +22585,7 @@
     </row>
     <row r="947" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A947" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B947" t="s">
         <v>718</v>
@@ -22604,12 +22601,12 @@
         <v>730</v>
       </c>
       <c r="F947" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="948" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A948" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B948" t="s">
         <v>719</v>
@@ -22627,7 +22624,7 @@
     </row>
     <row r="949" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A949" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B949" t="s">
         <v>718</v>
@@ -22644,7 +22641,7 @@
     </row>
     <row r="950" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A950" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B950" t="s">
         <v>718</v>
@@ -22787,7 +22784,7 @@
     </row>
     <row r="957" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A957" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B957" t="s">
         <v>720</v>
@@ -22824,12 +22821,12 @@
         <v>723</v>
       </c>
       <c r="F958" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="959" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A959" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B959" t="s">
         <v>720</v>
@@ -22845,7 +22842,7 @@
         <v>723</v>
       </c>
       <c r="F959" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="960" spans="1:6" x14ac:dyDescent="0.35">
@@ -22866,7 +22863,7 @@
         <v>723</v>
       </c>
       <c r="F960" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="961" spans="1:6" x14ac:dyDescent="0.35">
@@ -22907,7 +22904,7 @@
     </row>
     <row r="963" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A963" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B963" t="s">
         <v>720</v>
@@ -22944,7 +22941,7 @@
         <v>723</v>
       </c>
       <c r="F964" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="965" spans="1:6" x14ac:dyDescent="0.35">
@@ -23001,7 +22998,7 @@
         <v>723</v>
       </c>
       <c r="F967" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="968" spans="1:6" x14ac:dyDescent="0.35">
@@ -23043,7 +23040,7 @@
         <v>723</v>
       </c>
       <c r="F969" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="970" spans="1:6" x14ac:dyDescent="0.35">
@@ -23064,7 +23061,7 @@
         <v>723</v>
       </c>
       <c r="F970" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="971" spans="1:6" x14ac:dyDescent="0.35">
@@ -23085,12 +23082,12 @@
         <v>723</v>
       </c>
       <c r="F971" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="972" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A972" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B972" t="s">
         <v>720</v>
@@ -23106,7 +23103,7 @@
         <v>723</v>
       </c>
       <c r="F972" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="973" spans="1:6" x14ac:dyDescent="0.35">
@@ -23127,12 +23124,12 @@
         <v>723</v>
       </c>
       <c r="F973" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="974" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A974" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B974" t="s">
         <v>720</v>
@@ -23190,7 +23187,7 @@
         <v>723</v>
       </c>
       <c r="F976" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="977" spans="1:6" x14ac:dyDescent="0.35">
@@ -23274,12 +23271,12 @@
         <v>723</v>
       </c>
       <c r="F980" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="981" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A981" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B981" t="s">
         <v>720</v>
@@ -23316,7 +23313,7 @@
         <v>721</v>
       </c>
       <c r="F982" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="983" spans="1:6" x14ac:dyDescent="0.35">
@@ -23337,12 +23334,12 @@
         <v>724</v>
       </c>
       <c r="F983" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="984" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A984" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B984" t="s">
         <v>720</v>
@@ -23358,7 +23355,7 @@
         <v>723</v>
       </c>
       <c r="F984" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="985" spans="1:6" x14ac:dyDescent="0.35">
@@ -23369,8 +23366,8 @@
         <v>720</v>
       </c>
       <c r="C985">
-        <f>1/4.28</f>
-        <v>0.23364485981308411</v>
+        <f>3.6/19</f>
+        <v>0.18947368421052632</v>
       </c>
       <c r="D985" t="s">
         <v>721</v>
@@ -23379,7 +23376,7 @@
         <v>723</v>
       </c>
       <c r="F985" t="s">
-        <v>821</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="986" spans="1:6" x14ac:dyDescent="0.35">
@@ -23390,8 +23387,8 @@
         <v>720</v>
       </c>
       <c r="C986">
-        <f>1/4.28</f>
-        <v>0.23364485981308411</v>
+        <f>3.6/19</f>
+        <v>0.18947368421052632</v>
       </c>
       <c r="D986" t="s">
         <v>721</v>
@@ -23400,7 +23397,7 @@
         <v>723</v>
       </c>
       <c r="F986" t="s">
-        <v>821</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="987" spans="1:6" x14ac:dyDescent="0.35">
@@ -23411,8 +23408,8 @@
         <v>720</v>
       </c>
       <c r="C987">
-        <f>1/4.28</f>
-        <v>0.23364485981308411</v>
+        <f>3.6/19</f>
+        <v>0.18947368421052632</v>
       </c>
       <c r="D987" t="s">
         <v>721</v>
@@ -23421,7 +23418,7 @@
         <v>723</v>
       </c>
       <c r="F987" t="s">
-        <v>821</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="988" spans="1:6" x14ac:dyDescent="0.35">
@@ -23541,7 +23538,7 @@
         <v>725</v>
       </c>
       <c r="F993" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="994" spans="1:6" x14ac:dyDescent="0.35">
@@ -23583,7 +23580,7 @@
         <v>725</v>
       </c>
       <c r="F995" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="996" spans="1:6" x14ac:dyDescent="0.35">
@@ -23625,7 +23622,7 @@
         <v>725</v>
       </c>
       <c r="F997" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="998" spans="1:6" x14ac:dyDescent="0.35">
@@ -23667,7 +23664,7 @@
         <v>725</v>
       </c>
       <c r="F999" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1000" spans="1:6" x14ac:dyDescent="0.35">
@@ -23709,7 +23706,7 @@
         <v>725</v>
       </c>
       <c r="F1001" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1002" spans="1:6" x14ac:dyDescent="0.35">
@@ -23751,7 +23748,7 @@
         <v>725</v>
       </c>
       <c r="F1003" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1004" spans="1:6" x14ac:dyDescent="0.35">
@@ -23793,7 +23790,7 @@
         <v>725</v>
       </c>
       <c r="F1005" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1006" spans="1:6" x14ac:dyDescent="0.35">
@@ -23835,7 +23832,7 @@
         <v>725</v>
       </c>
       <c r="F1007" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1008" spans="1:6" x14ac:dyDescent="0.35">
@@ -23877,7 +23874,7 @@
         <v>725</v>
       </c>
       <c r="F1009" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1010" spans="1:6" x14ac:dyDescent="0.35">
@@ -23919,7 +23916,7 @@
         <v>725</v>
       </c>
       <c r="F1011" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1012" spans="1:6" x14ac:dyDescent="0.35">
@@ -23961,7 +23958,7 @@
         <v>725</v>
       </c>
       <c r="F1013" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1014" spans="1:6" x14ac:dyDescent="0.35">
@@ -24003,7 +24000,7 @@
         <v>725</v>
       </c>
       <c r="F1015" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1016" spans="1:6" x14ac:dyDescent="0.35">
@@ -24045,7 +24042,7 @@
         <v>725</v>
       </c>
       <c r="F1017" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1018" spans="1:6" x14ac:dyDescent="0.35">
@@ -24087,7 +24084,7 @@
         <v>725</v>
       </c>
       <c r="F1019" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1020" spans="1:6" x14ac:dyDescent="0.35">
@@ -24129,7 +24126,7 @@
         <v>725</v>
       </c>
       <c r="F1021" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1022" spans="1:6" x14ac:dyDescent="0.35">
@@ -24171,7 +24168,7 @@
         <v>725</v>
       </c>
       <c r="F1023" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1024" spans="1:6" x14ac:dyDescent="0.35">
@@ -24192,7 +24189,7 @@
         <v>730</v>
       </c>
       <c r="F1024" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="1025" spans="1:6" x14ac:dyDescent="0.35">
@@ -24231,7 +24228,7 @@
         <v>730</v>
       </c>
       <c r="F1026" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="1027" spans="1:6" x14ac:dyDescent="0.35">
@@ -24504,7 +24501,7 @@
         <v>730</v>
       </c>
       <c r="F1040" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="1041" spans="1:6" x14ac:dyDescent="0.35">
@@ -24543,7 +24540,7 @@
         <v>730</v>
       </c>
       <c r="F1042" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="1043" spans="1:6" x14ac:dyDescent="0.35">
@@ -24620,7 +24617,7 @@
         <v>730</v>
       </c>
       <c r="F1046" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="1047" spans="1:6" x14ac:dyDescent="0.35">
@@ -24641,7 +24638,7 @@
         <v>723</v>
       </c>
       <c r="F1047" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="1048" spans="1:6" x14ac:dyDescent="0.35">
@@ -24713,7 +24710,7 @@
         <v>730</v>
       </c>
       <c r="F1051" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="1052" spans="1:6" x14ac:dyDescent="0.35">
@@ -24790,7 +24787,7 @@
         <v>722</v>
       </c>
       <c r="F1055" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="1056" spans="1:6" x14ac:dyDescent="0.35">
@@ -24811,7 +24808,7 @@
         <v>730</v>
       </c>
       <c r="F1056" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="1057" spans="1:6" x14ac:dyDescent="0.35">
@@ -25004,7 +25001,7 @@
         <v>730</v>
       </c>
       <c r="F1066" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="1067" spans="1:6" x14ac:dyDescent="0.35">
@@ -25025,7 +25022,7 @@
         <v>723</v>
       </c>
       <c r="F1067" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="1068" spans="1:6" x14ac:dyDescent="0.35">
@@ -25139,7 +25136,7 @@
         <v>730</v>
       </c>
       <c r="F1073" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="1074" spans="1:6" x14ac:dyDescent="0.35">
@@ -25178,7 +25175,7 @@
         <v>730</v>
       </c>
       <c r="F1075" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="1076" spans="1:6" x14ac:dyDescent="0.35">
@@ -25217,7 +25214,7 @@
         <v>730</v>
       </c>
       <c r="F1077" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="1078" spans="1:6" x14ac:dyDescent="0.35">
@@ -25256,7 +25253,7 @@
         <v>730</v>
       </c>
       <c r="F1079" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="1080" spans="1:6" x14ac:dyDescent="0.35">
@@ -25333,7 +25330,7 @@
         <v>730</v>
       </c>
       <c r="F1083" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="1084" spans="1:6" x14ac:dyDescent="0.35">
@@ -25354,7 +25351,7 @@
         <v>723</v>
       </c>
       <c r="F1084" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="1085" spans="1:6" x14ac:dyDescent="0.35">
@@ -25447,7 +25444,7 @@
         <v>729</v>
       </c>
       <c r="F1089" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="1090" spans="1:6" x14ac:dyDescent="0.35">
@@ -25489,7 +25486,7 @@
         <v>729</v>
       </c>
       <c r="F1091" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="1092" spans="1:6" x14ac:dyDescent="0.35">
@@ -25657,7 +25654,7 @@
         <v>723</v>
       </c>
       <c r="F1099" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="1100" spans="1:6" x14ac:dyDescent="0.35">
@@ -25699,7 +25696,7 @@
         <v>723</v>
       </c>
       <c r="F1101" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="1102" spans="1:6" x14ac:dyDescent="0.35">
@@ -25720,7 +25717,7 @@
         <v>730</v>
       </c>
       <c r="F1102" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="1103" spans="1:6" x14ac:dyDescent="0.35">
@@ -25762,7 +25759,7 @@
         <v>730</v>
       </c>
       <c r="F1104" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="1105" spans="1:6" x14ac:dyDescent="0.35">
@@ -25804,7 +25801,7 @@
         <v>730</v>
       </c>
       <c r="F1106" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="1107" spans="1:6" x14ac:dyDescent="0.35">
@@ -25867,7 +25864,7 @@
         <v>730</v>
       </c>
       <c r="F1109" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="1110" spans="1:6" x14ac:dyDescent="0.35">
@@ -25930,7 +25927,7 @@
         <v>730</v>
       </c>
       <c r="F1112" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="1113" spans="1:6" x14ac:dyDescent="0.35">
@@ -25993,7 +25990,7 @@
         <v>730</v>
       </c>
       <c r="F1115" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="1116" spans="1:6" x14ac:dyDescent="0.35">
@@ -26035,7 +26032,7 @@
         <v>730</v>
       </c>
       <c r="F1117" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="1118" spans="1:6" x14ac:dyDescent="0.35">
@@ -26077,7 +26074,7 @@
         <v>730</v>
       </c>
       <c r="F1119" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="1120" spans="1:6" x14ac:dyDescent="0.35">
@@ -26199,7 +26196,7 @@
         <v>723</v>
       </c>
       <c r="F1125" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="1126" spans="1:6" x14ac:dyDescent="0.35">
@@ -26220,7 +26217,7 @@
         <v>730</v>
       </c>
       <c r="F1126" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="1127" spans="1:6" x14ac:dyDescent="0.35">
@@ -26241,7 +26238,7 @@
         <v>723</v>
       </c>
       <c r="F1127" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1128" spans="1:6" x14ac:dyDescent="0.35">
@@ -26262,7 +26259,7 @@
         <v>730</v>
       </c>
       <c r="F1128" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="1129" spans="1:6" x14ac:dyDescent="0.35">
@@ -26283,7 +26280,7 @@
         <v>723</v>
       </c>
       <c r="F1129" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1130" spans="1:6" x14ac:dyDescent="0.35">
@@ -26460,7 +26457,7 @@
         <v>733</v>
       </c>
       <c r="F1138" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="1139" spans="1:6" x14ac:dyDescent="0.35">
@@ -26481,7 +26478,7 @@
         <v>729</v>
       </c>
       <c r="F1139" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="1140" spans="1:6" x14ac:dyDescent="0.35">
@@ -26502,7 +26499,7 @@
         <v>733</v>
       </c>
       <c r="F1140" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="1141" spans="1:6" x14ac:dyDescent="0.35">
@@ -26523,7 +26520,7 @@
         <v>729</v>
       </c>
       <c r="F1141" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="1142" spans="1:6" x14ac:dyDescent="0.35">
@@ -26565,7 +26562,7 @@
         <v>729</v>
       </c>
       <c r="F1143" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="1144" spans="1:6" x14ac:dyDescent="0.35">
@@ -26607,7 +26604,7 @@
         <v>725</v>
       </c>
       <c r="F1145" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1146" spans="1:6" x14ac:dyDescent="0.35">
@@ -26649,7 +26646,7 @@
         <v>725</v>
       </c>
       <c r="F1147" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1148" spans="1:6" x14ac:dyDescent="0.35">
@@ -26691,7 +26688,7 @@
         <v>725</v>
       </c>
       <c r="F1149" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1150" spans="1:6" x14ac:dyDescent="0.35">
@@ -26733,7 +26730,7 @@
         <v>725</v>
       </c>
       <c r="F1151" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1152" spans="1:6" x14ac:dyDescent="0.35">
@@ -26775,7 +26772,7 @@
         <v>725</v>
       </c>
       <c r="F1153" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1154" spans="1:6" x14ac:dyDescent="0.35">
@@ -26817,7 +26814,7 @@
         <v>725</v>
       </c>
       <c r="F1155" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1156" spans="1:6" x14ac:dyDescent="0.35">
@@ -26859,7 +26856,7 @@
         <v>725</v>
       </c>
       <c r="F1157" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1158" spans="1:6" x14ac:dyDescent="0.35">
@@ -26901,7 +26898,7 @@
         <v>725</v>
       </c>
       <c r="F1159" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1160" spans="1:6" x14ac:dyDescent="0.35">
@@ -26943,7 +26940,7 @@
         <v>725</v>
       </c>
       <c r="F1161" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1162" spans="1:6" x14ac:dyDescent="0.35">
@@ -26985,7 +26982,7 @@
         <v>725</v>
       </c>
       <c r="F1163" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1164" spans="1:6" x14ac:dyDescent="0.35">
@@ -27027,7 +27024,7 @@
         <v>725</v>
       </c>
       <c r="F1165" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1166" spans="1:6" x14ac:dyDescent="0.35">
@@ -27069,7 +27066,7 @@
         <v>725</v>
       </c>
       <c r="F1167" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="1168" spans="1:6" x14ac:dyDescent="0.35">
@@ -27168,7 +27165,7 @@
         <v>733</v>
       </c>
       <c r="F1172" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="1173" spans="1:6" x14ac:dyDescent="0.35">
@@ -27205,7 +27202,7 @@
         <v>722</v>
       </c>
       <c r="F1174" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="1175" spans="1:6" x14ac:dyDescent="0.35">
@@ -27225,7 +27222,7 @@
         <v>722</v>
       </c>
       <c r="F1175" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="1176" spans="1:6" x14ac:dyDescent="0.35">
@@ -27246,7 +27243,7 @@
         <v>733</v>
       </c>
       <c r="F1176" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="1177" spans="1:6" x14ac:dyDescent="0.35">
@@ -27283,7 +27280,7 @@
         <v>722</v>
       </c>
       <c r="F1178" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="1179" spans="1:6" x14ac:dyDescent="0.35">
@@ -27303,7 +27300,7 @@
         <v>722</v>
       </c>
       <c r="F1179" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="1180" spans="1:6" x14ac:dyDescent="0.35">
@@ -27324,7 +27321,7 @@
         <v>733</v>
       </c>
       <c r="F1180" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="1181" spans="1:6" x14ac:dyDescent="0.35">
@@ -27361,7 +27358,7 @@
         <v>722</v>
       </c>
       <c r="F1182" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="1183" spans="1:6" x14ac:dyDescent="0.35">
@@ -27381,7 +27378,7 @@
         <v>722</v>
       </c>
       <c r="F1183" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="1184" spans="1:6" x14ac:dyDescent="0.35">
@@ -27402,7 +27399,7 @@
         <v>733</v>
       </c>
       <c r="F1184" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="1185" spans="1:6" x14ac:dyDescent="0.35">
@@ -27439,7 +27436,7 @@
         <v>722</v>
       </c>
       <c r="F1186" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="1187" spans="1:6" x14ac:dyDescent="0.35">
@@ -27459,7 +27456,7 @@
         <v>722</v>
       </c>
       <c r="F1187" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="1188" spans="1:6" x14ac:dyDescent="0.35">
@@ -27558,7 +27555,7 @@
         <v>733</v>
       </c>
       <c r="F1192" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="1193" spans="1:6" x14ac:dyDescent="0.35">
@@ -27579,7 +27576,7 @@
         <v>729</v>
       </c>
       <c r="F1193" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="1194" spans="1:6" x14ac:dyDescent="0.35">
@@ -27621,7 +27618,7 @@
         <v>729</v>
       </c>
       <c r="F1195" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="1196" spans="1:6" x14ac:dyDescent="0.35">
@@ -27663,7 +27660,7 @@
         <v>729</v>
       </c>
       <c r="F1197" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="1198" spans="1:6" x14ac:dyDescent="0.35">
@@ -27689,7 +27686,7 @@
     </row>
     <row r="1199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1199" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B1199" t="s">
         <v>718</v>
@@ -27705,12 +27702,12 @@
         <v>730</v>
       </c>
       <c r="F1199" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="1200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1200" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B1200" t="s">
         <v>718</v>
@@ -27726,12 +27723,12 @@
         <v>730</v>
       </c>
       <c r="F1200" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="1201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1201" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B1201" t="s">
         <v>718</v>
@@ -27747,12 +27744,12 @@
         <v>730</v>
       </c>
       <c r="F1201" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="1202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1202" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B1202" t="s">
         <v>718</v>
@@ -27768,12 +27765,12 @@
         <v>730</v>
       </c>
       <c r="F1202" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="1203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1203" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B1203" t="s">
         <v>718</v>
@@ -27789,12 +27786,12 @@
         <v>730</v>
       </c>
       <c r="F1203" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="1204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1204" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B1204" t="s">
         <v>718</v>
@@ -27810,12 +27807,12 @@
         <v>730</v>
       </c>
       <c r="F1204" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="1205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1205" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B1205" t="s">
         <v>718</v>
@@ -27831,12 +27828,12 @@
         <v>730</v>
       </c>
       <c r="F1205" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="1206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1206" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B1206" t="s">
         <v>718</v>
@@ -27852,7 +27849,7 @@
         <v>730</v>
       </c>
       <c r="F1206" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="1207" spans="1:6" x14ac:dyDescent="0.35">
@@ -27860,7 +27857,7 @@
         <v>6</v>
       </c>
       <c r="B1207" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1207">
         <f>1 * 3.6 / 14.55</f>
@@ -27881,7 +27878,7 @@
         <v>7</v>
       </c>
       <c r="B1208" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1208">
         <f>1 / 8.22</f>
@@ -27902,7 +27899,7 @@
         <v>27</v>
       </c>
       <c r="B1209" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1209">
         <f>1 * 3.6 / 42.5</f>
@@ -27923,7 +27920,7 @@
         <v>53</v>
       </c>
       <c r="B1210" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1210">
         <f>1 / 10.5</f>
@@ -27944,7 +27941,7 @@
         <v>150</v>
       </c>
       <c r="B1211" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1211">
         <f>1 * 3.6 / 27.91</f>
@@ -27965,7 +27962,7 @@
         <v>227</v>
       </c>
       <c r="B1212" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1212">
         <f>1 / 11.83</f>
@@ -27986,7 +27983,7 @@
         <v>232</v>
       </c>
       <c r="B1213" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1213">
         <f>1</f>
@@ -28001,10 +27998,10 @@
     </row>
     <row r="1214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1214" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B1214" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1214">
         <f>1</f>
@@ -28019,10 +28016,10 @@
     </row>
     <row r="1215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1215" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B1215" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1215">
         <f>1</f>
@@ -28037,10 +28034,10 @@
     </row>
     <row r="1216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1216" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B1216" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1216">
         <f>1</f>
@@ -28058,7 +28055,7 @@
         <v>236</v>
       </c>
       <c r="B1217" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1217">
         <f>1 / 13.28</f>
@@ -28079,7 +28076,7 @@
         <v>240</v>
       </c>
       <c r="B1218" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1218">
         <f>1 * 3.6 / 31.58</f>
@@ -28100,7 +28097,7 @@
         <v>242</v>
       </c>
       <c r="B1219" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1219">
         <f>1 * 3.6 / 40.938</f>
@@ -28121,7 +28118,7 @@
         <v>243</v>
       </c>
       <c r="B1220" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1220">
         <f>1 * 3.6 / 50.285</f>
@@ -28142,7 +28139,7 @@
         <v>255</v>
       </c>
       <c r="B1221" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1221">
         <f>1 * 3.6 / 42.5</f>
@@ -28163,7 +28160,7 @@
         <v>262</v>
       </c>
       <c r="B1222" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1222">
         <f>1 / 33.3</f>
@@ -28184,7 +28181,7 @@
         <v>269</v>
       </c>
       <c r="B1223" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1223">
         <f>1 / 33.3</f>
@@ -28205,7 +28202,7 @@
         <v>270</v>
       </c>
       <c r="B1224" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1224">
         <f>1 / 33.3</f>
@@ -28226,7 +28223,7 @@
         <v>271</v>
       </c>
       <c r="B1225" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1225">
         <f>1 / 33.3</f>
@@ -28247,7 +28244,7 @@
         <v>307</v>
       </c>
       <c r="B1226" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1226">
         <f>1 * 3.6 / 43</f>
@@ -28268,7 +28265,7 @@
         <v>326</v>
       </c>
       <c r="B1227" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1227">
         <f>1 * 3.6 / 42.6</f>
@@ -28289,7 +28286,7 @@
         <v>327</v>
       </c>
       <c r="B1228" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1228">
         <f>1 * 3.6 / 39</f>
@@ -28310,7 +28307,7 @@
         <v>332</v>
       </c>
       <c r="B1229" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1229">
         <f>1 / 5.54</f>
@@ -28331,7 +28328,7 @@
         <v>344</v>
       </c>
       <c r="B1230" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1230">
         <f>1 * 3.6 / 39</f>
@@ -28352,7 +28349,7 @@
         <v>351</v>
       </c>
       <c r="B1231" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1231">
         <f t="shared" ref="C1231:C1232" si="0">1 * 3.6 / 39</f>
@@ -28373,7 +28370,7 @@
         <v>352</v>
       </c>
       <c r="B1232" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1232">
         <f t="shared" si="0"/>
@@ -28394,7 +28391,7 @@
         <v>353</v>
       </c>
       <c r="B1233" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1233">
         <f>1 * 3.6 / 46.5</f>
@@ -28415,7 +28412,7 @@
         <v>367</v>
       </c>
       <c r="B1234" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1234">
         <f>1</f>
@@ -28433,7 +28430,7 @@
         <v>374</v>
       </c>
       <c r="B1235" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1235">
         <f>1</f>
@@ -28451,7 +28448,7 @@
         <v>376</v>
       </c>
       <c r="B1236" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1236">
         <f>1 * 3.6 / 32.45</f>
@@ -28472,7 +28469,7 @@
         <v>381</v>
       </c>
       <c r="B1237" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1237">
         <f>1</f>
@@ -28490,7 +28487,7 @@
         <v>382</v>
       </c>
       <c r="B1238" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1238">
         <f>1 * 3.6 / 46.4</f>
@@ -28511,7 +28508,7 @@
         <v>383</v>
       </c>
       <c r="B1239" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1239">
         <f>1 * 3.6 / 45.799</f>
@@ -28532,7 +28529,7 @@
         <v>384</v>
       </c>
       <c r="B1240" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1240">
         <f>1</f>
@@ -28550,7 +28547,7 @@
         <v>385</v>
       </c>
       <c r="B1241" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1241">
         <f>1</f>
@@ -28568,7 +28565,7 @@
         <v>439</v>
       </c>
       <c r="B1242" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1242">
         <f>1</f>
@@ -28586,7 +28583,7 @@
         <v>490</v>
       </c>
       <c r="B1243" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1243">
         <f>1 * 3.6 / 42.43</f>
@@ -28607,7 +28604,7 @@
         <v>561</v>
       </c>
       <c r="B1244" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1244">
         <f>1 * 3.6 / (3900*1000)</f>
@@ -28628,7 +28625,7 @@
         <v>562</v>
       </c>
       <c r="B1245" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1245">
         <f>-1 * 3.6 / 12.35</f>
@@ -28649,7 +28646,7 @@
         <v>563</v>
       </c>
       <c r="B1246" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1246">
         <f>-1 * 3.6 / (6.087*0.95)</f>
@@ -28670,7 +28667,7 @@
         <v>564</v>
       </c>
       <c r="B1247" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1247">
         <f>-1 * 3.6 / 2.453</f>
@@ -28691,7 +28688,7 @@
         <v>565</v>
       </c>
       <c r="B1248" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1248">
         <f>1 * 3.6 / (0.95*15)</f>
@@ -28704,7 +28701,7 @@
         <v>723</v>
       </c>
       <c r="F1248" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="1249" spans="1:6" x14ac:dyDescent="0.35">
@@ -28712,7 +28709,7 @@
         <v>572</v>
       </c>
       <c r="B1249" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1249">
         <f>1 * 3.6 / 15.4</f>
@@ -28733,7 +28730,7 @@
         <v>574</v>
       </c>
       <c r="B1250" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1250">
         <f>1 * 3.6 / 40.961</f>
@@ -28754,7 +28751,7 @@
         <v>716</v>
       </c>
       <c r="B1251" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1251">
         <f>1 * 3.6 / 31.58</f>
@@ -28772,10 +28769,10 @@
     </row>
     <row r="1252" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1252" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B1252" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1252">
         <f>1 * 3.6 / 43</f>
@@ -28793,10 +28790,10 @@
     </row>
     <row r="1253" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1253" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B1253" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1253">
         <f>1 * 3.6 / 42.6</f>
@@ -28814,10 +28811,10 @@
     </row>
     <row r="1254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1254" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B1254" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1254">
         <f>1 / 5.54</f>
@@ -28838,7 +28835,7 @@
         <v>428</v>
       </c>
       <c r="B1255" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1255">
         <f>1 * 3.6 / 39</f>
@@ -28856,10 +28853,10 @@
     </row>
     <row r="1256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1256" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B1256" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1256">
         <f>1 / (0.777 * 13.1)</f>
@@ -28877,10 +28874,10 @@
     </row>
     <row r="1257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1257" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B1257" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1257">
         <f>1 / (0.777 * 13.1)</f>
@@ -28898,10 +28895,10 @@
     </row>
     <row r="1258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1258" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B1258" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1258">
         <f>1 / (0.777 * 13.1)</f>
@@ -28919,10 +28916,10 @@
     </row>
     <row r="1259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1259" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B1259" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1259">
         <f>1 * 3.6</f>
@@ -28937,10 +28934,10 @@
     </row>
     <row r="1260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1260" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B1260" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1260">
         <f>1 * 3.6</f>
@@ -28955,10 +28952,10 @@
     </row>
     <row r="1261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1261" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B1261" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1261">
         <v>1</v>
@@ -28972,10 +28969,10 @@
     </row>
     <row r="1262" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1262" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B1262" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1262">
         <v>1</v>
@@ -28989,10 +28986,10 @@
     </row>
     <row r="1263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1263" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B1263" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1263">
         <v>1</v>
@@ -29006,7 +29003,7 @@
     </row>
     <row r="1264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1264" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B1264" t="s">
         <v>717</v>
@@ -29022,12 +29019,12 @@
         <v>723</v>
       </c>
       <c r="F1264" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="1265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1265" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B1265" t="s">
         <v>717</v>
@@ -29043,12 +29040,12 @@
         <v>723</v>
       </c>
       <c r="F1265" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="1266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1266" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B1266" t="s">
         <v>717</v>
@@ -29064,12 +29061,12 @@
         <v>723</v>
       </c>
       <c r="F1266" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="1267" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1267" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B1267" t="s">
         <v>717</v>
@@ -29085,12 +29082,12 @@
         <v>723</v>
       </c>
       <c r="F1267" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="1268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1268" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B1268" t="s">
         <v>717</v>
@@ -29106,12 +29103,12 @@
         <v>723</v>
       </c>
       <c r="F1268" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="1269" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1269" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B1269" t="s">
         <v>717</v>
@@ -29127,12 +29124,12 @@
         <v>723</v>
       </c>
       <c r="F1269" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="1270" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1270" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B1270" t="s">
         <v>717</v>
@@ -29148,12 +29145,12 @@
         <v>723</v>
       </c>
       <c r="F1270" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="1271" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1271" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B1271" t="s">
         <v>717</v>
@@ -29169,12 +29166,12 @@
         <v>723</v>
       </c>
       <c r="F1271" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="1272" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1272" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B1272" t="s">
         <v>717</v>
@@ -29190,12 +29187,12 @@
         <v>723</v>
       </c>
       <c r="F1272" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="1273" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1273" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B1273" t="s">
         <v>717</v>
@@ -29211,12 +29208,12 @@
         <v>723</v>
       </c>
       <c r="F1273" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="1274" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1274" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B1274" t="s">
         <v>717</v>
@@ -29232,15 +29229,15 @@
         <v>723</v>
       </c>
       <c r="F1274" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="1275" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1275" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B1275" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1275">
         <f>3.6/18.43</f>
@@ -29253,15 +29250,15 @@
         <v>723</v>
       </c>
       <c r="F1275" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="1276" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1276" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B1276" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1276">
         <f>3.6/18.61</f>
@@ -29274,15 +29271,15 @@
         <v>723</v>
       </c>
       <c r="F1276" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="1277" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1277" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B1277" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1277">
         <f>3.6/19.06</f>
@@ -29295,15 +29292,15 @@
         <v>723</v>
       </c>
       <c r="F1277" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="1278" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1278" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B1278" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1278">
         <f>3.6/18.93</f>
@@ -29316,15 +29313,15 @@
         <v>723</v>
       </c>
       <c r="F1278" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="1279" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1279" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B1279" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1279">
         <f>3.6 / 7.09</f>
@@ -29337,15 +29334,15 @@
         <v>723</v>
       </c>
       <c r="F1279" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="1280" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1280" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B1280" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1280">
         <f>3.6/15.34</f>
@@ -29358,15 +29355,15 @@
         <v>723</v>
       </c>
       <c r="F1280" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="1281" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1281" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B1281" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1281">
         <f>-1 * 3.6 / 17.09</f>
@@ -29379,15 +29376,15 @@
         <v>723</v>
       </c>
       <c r="F1281" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="1282" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1282" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B1282" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1282">
         <f>3.6/15.98</f>
@@ -29400,15 +29397,15 @@
         <v>723</v>
       </c>
       <c r="F1282" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="1283" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1283" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B1283" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1283">
         <f>-1 * 3.6 / 11.24</f>
@@ -29421,15 +29418,15 @@
         <v>723</v>
       </c>
       <c r="F1283" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="1284" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1284" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B1284" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1284">
         <f>3.6/18.63</f>
@@ -29442,15 +29439,15 @@
         <v>723</v>
       </c>
       <c r="F1284" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="1285" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1285" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B1285" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1285">
         <f>-1 * 3.6 / 7.64</f>
@@ -29463,12 +29460,12 @@
         <v>723</v>
       </c>
       <c r="F1285" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="1286" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1286" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B1286" t="s">
         <v>717</v>
@@ -29484,15 +29481,15 @@
         <v>723</v>
       </c>
       <c r="F1286" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="1287" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1287" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B1287" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1287">
         <f>1/10.83</f>
@@ -29505,12 +29502,12 @@
         <v>723</v>
       </c>
       <c r="F1287" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="1288" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1288" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B1288" t="s">
         <v>717</v>
@@ -29526,15 +29523,15 @@
         <v>723</v>
       </c>
       <c r="F1288" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="1289" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1289" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B1289" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C1289">
         <f>1/10.83</f>
@@ -29547,12 +29544,12 @@
         <v>723</v>
       </c>
       <c r="F1289" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="1290" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1290" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B1290" t="s">
         <v>718</v>
@@ -29568,12 +29565,12 @@
         <v>733</v>
       </c>
       <c r="F1290" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="1291" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1291" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B1291" t="s">
         <v>719</v>
@@ -29590,7 +29587,7 @@
     </row>
     <row r="1292" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1292" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B1292" t="s">
         <v>718</v>
@@ -29606,12 +29603,12 @@
         <v>733</v>
       </c>
       <c r="F1292" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="1293" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1293" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B1293" t="s">
         <v>719</v>
@@ -29628,7 +29625,7 @@
     </row>
     <row r="1294" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1294" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B1294" t="s">
         <v>718</v>
@@ -29644,12 +29641,12 @@
         <v>733</v>
       </c>
       <c r="F1294" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="1295" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1295" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B1295" t="s">
         <v>719</v>
@@ -29666,7 +29663,7 @@
     </row>
     <row r="1296" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1296" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B1296" t="s">
         <v>718</v>
@@ -29682,12 +29679,12 @@
         <v>733</v>
       </c>
       <c r="F1296" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="1297" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1297" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B1297" t="s">
         <v>719</v>
@@ -29704,7 +29701,7 @@
     </row>
     <row r="1298" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1298" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B1298" t="s">
         <v>718</v>
@@ -29720,12 +29717,12 @@
         <v>733</v>
       </c>
       <c r="F1298" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="1299" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1299" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B1299" t="s">
         <v>719</v>
@@ -29742,7 +29739,7 @@
     </row>
     <row r="1300" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1300" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B1300" t="s">
         <v>718</v>
@@ -29758,12 +29755,12 @@
         <v>733</v>
       </c>
       <c r="F1300" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="1301" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1301" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B1301" t="s">
         <v>719</v>
@@ -29780,7 +29777,7 @@
     </row>
     <row r="1302" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1302" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B1302" t="s">
         <v>718</v>
@@ -29796,12 +29793,12 @@
         <v>733</v>
       </c>
       <c r="F1302" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="1303" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1303" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B1303" t="s">
         <v>719</v>
@@ -29818,7 +29815,7 @@
     </row>
     <row r="1304" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1304" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B1304" t="s">
         <v>718</v>
@@ -29834,12 +29831,12 @@
         <v>733</v>
       </c>
       <c r="F1304" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="1305" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1305" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B1305" t="s">
         <v>719</v>
@@ -29856,7 +29853,7 @@
     </row>
     <row r="1306" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1306" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B1306" t="s">
         <v>718</v>
@@ -29872,12 +29869,12 @@
         <v>733</v>
       </c>
       <c r="F1306" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="1307" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1307" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B1307" t="s">
         <v>719</v>
@@ -29894,7 +29891,7 @@
     </row>
     <row r="1308" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1308" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B1308" t="s">
         <v>718</v>
@@ -29910,12 +29907,12 @@
         <v>733</v>
       </c>
       <c r="F1308" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="1309" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1309" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B1309" t="s">
         <v>719</v>
@@ -29932,7 +29929,7 @@
     </row>
     <row r="1310" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1310" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B1310" t="s">
         <v>718</v>
@@ -29948,12 +29945,12 @@
         <v>733</v>
       </c>
       <c r="F1310" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="1311" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1311" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B1311" t="s">
         <v>719</v>
@@ -29970,7 +29967,7 @@
     </row>
     <row r="1312" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1312" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B1312" t="s">
         <v>718</v>
@@ -29986,12 +29983,12 @@
         <v>733</v>
       </c>
       <c r="F1312" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="1313" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1313" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B1313" t="s">
         <v>719</v>
@@ -30008,7 +30005,7 @@
     </row>
     <row r="1314" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1314" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B1314" t="s">
         <v>719</v>
@@ -30025,7 +30022,7 @@
     </row>
     <row r="1315" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1315" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B1315" t="s">
         <v>719</v>
@@ -30042,7 +30039,7 @@
     </row>
     <row r="1316" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1316" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B1316" t="s">
         <v>719</v>
@@ -30059,7 +30056,7 @@
     </row>
     <row r="1317" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1317" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B1317" t="s">
         <v>719</v>
@@ -30076,7 +30073,7 @@
     </row>
     <row r="1318" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1318" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B1318" t="s">
         <v>719</v>
